--- a/docs/Example Files/CRYSS V2.0 Input File Templates/3 Component Mixture.xlsx
+++ b/docs/Example Files/CRYSS V2.0 Input File Templates/3 Component Mixture.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\06 website\idiocratease-iggy.github.io\docs\Example Files\CRYSS V2.0 Input File Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593B3C93-337F-43A9-ACB0-91D41948201F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80EC845-347F-45AA-8088-6C3ED65D7C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16785" yWindow="1455" windowWidth="32730" windowHeight="13530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2616" yWindow="0" windowWidth="31980" windowHeight="16116" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="slice_records" sheetId="1" r:id="rId1"/>
+    <sheet name="CRYSS Input File V2.0" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -240,40 +240,40 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -579,39 +579,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="7"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="6" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="12" t="s">
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="8" t="s">
+      <c r="I1" s="10"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -632,35 +632,35 @@
       <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -671,7 +671,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -682,7 +682,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -693,7 +693,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -704,7 +704,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -715,7 +715,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -726,7 +726,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -737,7 +737,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -748,7 +748,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -759,7 +759,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -770,7 +770,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
